--- a/artfynd/A 11174-2026 artfynd.xlsx
+++ b/artfynd/A 11174-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80499304</v>
+        <v>80499293</v>
       </c>
       <c r="B2" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510628.1334729622</v>
+        <v>510628</v>
       </c>
       <c r="R2" t="n">
-        <v>6953040.996690108</v>
+        <v>6953041</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2019-06-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-06-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80499293</v>
+        <v>80499304</v>
       </c>
       <c r="B3" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510628.1334729622</v>
+        <v>510628</v>
       </c>
       <c r="R3" t="n">
-        <v>6953040.996690108</v>
+        <v>6953041</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,19 +847,9 @@
           <t>2019-06-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-06-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
